--- a/develop/ValueSet-mii-vs-prozedur-ops.xlsx
+++ b/develop/ValueSet-mii-vs-prozedur-ops.xlsx
@@ -23,12 +23,13 @@
     <sheet name="Include #13" r:id="rId17" sheetId="15"/>
     <sheet name="Include #14" r:id="rId18" sheetId="16"/>
     <sheet name="Include #15" r:id="rId19" sheetId="17"/>
+    <sheet name="Include #16" r:id="rId20" sheetId="18"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="34">
   <si>
     <t>Property</t>
   </si>
@@ -75,7 +76,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-17</t>
+    <t>2026-05-08</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -713,6 +714,46 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:B4"/>

--- a/develop/ValueSet-mii-vs-prozedur-ops.xlsx
+++ b/develop/ValueSet-mii-vs-prozedur-ops.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="35">
   <si>
     <t>Property</t>
   </si>
@@ -76,7 +76,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08</t>
+    <t>2026-06-15</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -104,6 +104,9 @@
   </si>
   <si>
     <t>Purpose</t>
+  </si>
+  <si>
+    <t>Define OPS codes allowed for procedure coding.</t>
   </si>
   <si>
     <t>Copyright</t>
@@ -371,22 +374,24 @@
       <c r="A13" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="B13" s="2"/>
+      <c r="B13" t="s" s="2">
+        <v>25</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -405,28 +410,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -445,28 +450,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -485,28 +490,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -525,28 +530,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -565,28 +570,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -605,28 +610,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -645,28 +650,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -685,28 +690,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -725,28 +730,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -765,28 +770,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -805,28 +810,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -845,28 +850,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -885,28 +890,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -925,28 +930,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -965,28 +970,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1005,28 +1010,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1045,28 +1050,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
